--- a/sensitivity_results/legacy/Inception_v3_Correlation_matrices.xlsx
+++ b/sensitivity_results/legacy/Inception_v3_Correlation_matrices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\ToGIT\Legacy\pearson_corelation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E91D562-FBDB-40AD-B837-BADE66D79540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FBD3FD-0221-4C38-9A56-A9CD0FB91545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sensitivity" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="44">
   <si>
     <t>Deer</t>
   </si>
@@ -175,7 +175,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,9 +190,23 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,6 +217,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -227,20 +249,62 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -538,10 +602,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CB458C-7C41-4EAF-AE37-5693C35E05AC}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="28.6328125" bestFit="1" customWidth="1"/>
@@ -971,12 +1035,12 @@
       <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="b">
+      <c r="B7" s="3" t="b">
         <f>IF(AND(B2&gt;0,B3&gt;0,B4&gt;0),TRUE,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C7" t="b">
-        <f t="shared" ref="B7:T7" si="1">IF(AND(C2&gt;0,C3&gt;0,C4&gt;0),TRUE,FALSE)</f>
+        <f t="shared" ref="C7:T7" si="1">IF(AND(C2&gt;0,C3&gt;0,C4&gt;0),TRUE,FALSE)</f>
         <v>1</v>
       </c>
       <c r="D7" t="b">
@@ -1011,23 +1075,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="b">
+      <c r="L7" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="M7" s="2" t="b">
+      <c r="M7" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N7" s="2" t="b">
+      <c r="N7" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="O7" s="2" t="b">
+      <c r="O7" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P7" s="2" t="b">
+      <c r="P7" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1039,11 +1103,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S7" s="2" t="b">
+      <c r="S7" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="T7" s="2" t="b">
+      <c r="T7" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1129,7 +1193,1805 @@
         <v>1</v>
       </c>
     </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <f>C22+1</f>
+        <v>2</v>
+      </c>
+      <c r="E22" s="4">
+        <f>D22+1</f>
+        <v>3</v>
+      </c>
+      <c r="F22" s="4">
+        <f>E22+1</f>
+        <v>4</v>
+      </c>
+      <c r="G22" s="4">
+        <f>F22+1</f>
+        <v>5</v>
+      </c>
+      <c r="H22" s="4">
+        <f>G22+1</f>
+        <v>6</v>
+      </c>
+      <c r="I22" s="4">
+        <f>H22+1</f>
+        <v>7</v>
+      </c>
+      <c r="J22" s="4">
+        <f>I22+1</f>
+        <v>8</v>
+      </c>
+      <c r="K22" s="4">
+        <f>J22+1</f>
+        <v>9</v>
+      </c>
+      <c r="L22" s="4">
+        <f>K22+1</f>
+        <v>10</v>
+      </c>
+      <c r="M22" s="4">
+        <f>L22+1</f>
+        <v>11</v>
+      </c>
+      <c r="N22" s="4">
+        <f>M22+1</f>
+        <v>12</v>
+      </c>
+      <c r="O22" s="4">
+        <f>N22+1</f>
+        <v>13</v>
+      </c>
+      <c r="P22" s="4">
+        <f>O22+1</f>
+        <v>14</v>
+      </c>
+      <c r="Q22" s="4">
+        <f>P22+1</f>
+        <v>15</v>
+      </c>
+      <c r="R22" s="4">
+        <f>Q22+1</f>
+        <v>16</v>
+      </c>
+      <c r="S22" s="4">
+        <f>R22+1</f>
+        <v>17</v>
+      </c>
+      <c r="T22" s="4">
+        <f>S22+1</f>
+        <v>18</v>
+      </c>
+      <c r="U22" s="4">
+        <f>T22+1</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="5" t="str">
+        <f>IF(MIN(Class_0!B2,Class_1!B2,Class_2!B2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C23" s="5" t="str">
+        <f>IF(MIN(Class_0!C2,Class_1!C2,Class_2!C2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D23" s="5" t="str">
+        <f>IF(MIN(Class_0!D2,Class_1!D2,Class_2!D2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E23" s="5" t="str">
+        <f>IF(MIN(Class_0!E2,Class_1!E2,Class_2!E2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F23" s="5" t="str">
+        <f>IF(MIN(Class_0!F2,Class_1!F2,Class_2!F2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G23" s="5" t="str">
+        <f>IF(MIN(Class_0!G2,Class_1!G2,Class_2!G2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H23" s="5" t="str">
+        <f>IF(MIN(Class_0!H2,Class_1!H2,Class_2!H2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I23" s="5" t="str">
+        <f>IF(MIN(Class_0!I2,Class_1!I2,Class_2!I2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J23" s="5" t="str">
+        <f>IF(MIN(Class_0!J2,Class_1!J2,Class_2!J2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K23" s="5" t="str">
+        <f>IF(MIN(Class_0!K2,Class_1!K2,Class_2!K2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L23" s="5" t="str">
+        <f>IF(MIN(Class_0!L2,Class_1!L2,Class_2!L2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M23" s="5" t="str">
+        <f>IF(MIN(Class_0!M2,Class_1!M2,Class_2!M2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N23" s="5" t="str">
+        <f>IF(MIN(Class_0!N2,Class_1!N2,Class_2!N2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O23" s="5" t="str">
+        <f>IF(MIN(Class_0!O2,Class_1!O2,Class_2!O2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P23" s="5" t="str">
+        <f>IF(MIN(Class_0!P2,Class_1!P2,Class_2!P2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q23" s="5" t="str">
+        <f>IF(MIN(Class_0!Q2,Class_1!Q2,Class_2!Q2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R23" s="5" t="str">
+        <f>IF(MIN(Class_0!R2,Class_1!R2,Class_2!R2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S23" s="5" t="str">
+        <f>IF(MIN(Class_0!S2,Class_1!S2,Class_2!S2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T23" s="5" t="str">
+        <f>IF(MIN(Class_0!T2,Class_1!T2,Class_2!T2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U23" s="5" t="str">
+        <f>IF(MIN(Class_0!U2,Class_1!U2,Class_2!U2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="5" t="str">
+        <f>IF(MIN(Class_0!B3,Class_1!B3,Class_2!B3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C24" s="5" t="str">
+        <f>IF(MIN(Class_0!C3,Class_1!C3,Class_2!C3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D24" s="5" t="str">
+        <f>IF(MIN(Class_0!D3,Class_1!D3,Class_2!D3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E24" s="5" t="str">
+        <f>IF(MIN(Class_0!E3,Class_1!E3,Class_2!E3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F24" s="5" t="str">
+        <f>IF(MIN(Class_0!F3,Class_1!F3,Class_2!F3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G24" s="5" t="str">
+        <f>IF(MIN(Class_0!G3,Class_1!G3,Class_2!G3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H24" s="5" t="str">
+        <f>IF(MIN(Class_0!H3,Class_1!H3,Class_2!H3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I24" s="5" t="str">
+        <f>IF(MIN(Class_0!I3,Class_1!I3,Class_2!I3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J24" s="5" t="str">
+        <f>IF(MIN(Class_0!J3,Class_1!J3,Class_2!J3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K24" s="5" t="str">
+        <f>IF(MIN(Class_0!K3,Class_1!K3,Class_2!K3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L24" s="5" t="str">
+        <f>IF(MIN(Class_0!L3,Class_1!L3,Class_2!L3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M24" s="5" t="str">
+        <f>IF(MIN(Class_0!M3,Class_1!M3,Class_2!M3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N24" s="5" t="str">
+        <f>IF(MIN(Class_0!N3,Class_1!N3,Class_2!N3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O24" s="5" t="str">
+        <f>IF(MIN(Class_0!O3,Class_1!O3,Class_2!O3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P24" s="5" t="str">
+        <f>IF(MIN(Class_0!P3,Class_1!P3,Class_2!P3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q24" s="5" t="str">
+        <f>IF(MIN(Class_0!Q3,Class_1!Q3,Class_2!Q3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R24" s="5" t="str">
+        <f>IF(MIN(Class_0!R3,Class_1!R3,Class_2!R3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S24" s="5" t="str">
+        <f>IF(MIN(Class_0!S3,Class_1!S3,Class_2!S3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T24" s="5" t="str">
+        <f>IF(MIN(Class_0!T3,Class_1!T3,Class_2!T3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U24" s="5" t="str">
+        <f>IF(MIN(Class_0!U3,Class_1!U3,Class_2!U3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="5" t="str">
+        <f>IF(MIN(Class_0!B4,Class_1!B4,Class_2!B4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C25" s="5" t="str">
+        <f>IF(MIN(Class_0!C4,Class_1!C4,Class_2!C4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="D25" s="5" t="str">
+        <f>IF(MIN(Class_0!D4,Class_1!D4,Class_2!D4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E25" s="5" t="str">
+        <f>IF(MIN(Class_0!E4,Class_1!E4,Class_2!E4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F25" s="5" t="str">
+        <f>IF(MIN(Class_0!F4,Class_1!F4,Class_2!F4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G25" s="5" t="str">
+        <f>IF(MIN(Class_0!G4,Class_1!G4,Class_2!G4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H25" s="5" t="str">
+        <f>IF(MIN(Class_0!H4,Class_1!H4,Class_2!H4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I25" s="5" t="str">
+        <f>IF(MIN(Class_0!I4,Class_1!I4,Class_2!I4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J25" s="5" t="str">
+        <f>IF(MIN(Class_0!J4,Class_1!J4,Class_2!J4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K25" s="5" t="str">
+        <f>IF(MIN(Class_0!K4,Class_1!K4,Class_2!K4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L25" s="5" t="str">
+        <f>IF(MIN(Class_0!L4,Class_1!L4,Class_2!L4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M25" s="5" t="str">
+        <f>IF(MIN(Class_0!M4,Class_1!M4,Class_2!M4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N25" s="5" t="str">
+        <f>IF(MIN(Class_0!N4,Class_1!N4,Class_2!N4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O25" s="5" t="str">
+        <f>IF(MIN(Class_0!O4,Class_1!O4,Class_2!O4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P25" s="5" t="str">
+        <f>IF(MIN(Class_0!P4,Class_1!P4,Class_2!P4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q25" s="5" t="str">
+        <f>IF(MIN(Class_0!Q4,Class_1!Q4,Class_2!Q4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R25" s="5" t="str">
+        <f>IF(MIN(Class_0!R4,Class_1!R4,Class_2!R4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S25" s="5" t="str">
+        <f>IF(MIN(Class_0!S4,Class_1!S4,Class_2!S4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T25" s="5" t="str">
+        <f>IF(MIN(Class_0!T4,Class_1!T4,Class_2!T4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U25" s="5" t="str">
+        <f>IF(MIN(Class_0!U4,Class_1!U4,Class_2!U4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="5" t="str">
+        <f>IF(MIN(Class_0!B5,Class_1!B5,Class_2!B5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C26" s="5" t="str">
+        <f>IF(MIN(Class_0!C5,Class_1!C5,Class_2!C5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="D26" s="5" t="str">
+        <f>IF(MIN(Class_0!D5,Class_1!D5,Class_2!D5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E26" s="5" t="str">
+        <f>IF(MIN(Class_0!E5,Class_1!E5,Class_2!E5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F26" s="5" t="str">
+        <f>IF(MIN(Class_0!F5,Class_1!F5,Class_2!F5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G26" s="5" t="str">
+        <f>IF(MIN(Class_0!G5,Class_1!G5,Class_2!G5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H26" s="5" t="str">
+        <f>IF(MIN(Class_0!H5,Class_1!H5,Class_2!H5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I26" s="5" t="str">
+        <f>IF(MIN(Class_0!I5,Class_1!I5,Class_2!I5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J26" s="5" t="str">
+        <f>IF(MIN(Class_0!J5,Class_1!J5,Class_2!J5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K26" s="5" t="str">
+        <f>IF(MIN(Class_0!K5,Class_1!K5,Class_2!K5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L26" s="5" t="str">
+        <f>IF(MIN(Class_0!L5,Class_1!L5,Class_2!L5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M26" s="5" t="str">
+        <f>IF(MIN(Class_0!M5,Class_1!M5,Class_2!M5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N26" s="5" t="str">
+        <f>IF(MIN(Class_0!N5,Class_1!N5,Class_2!N5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O26" s="5" t="str">
+        <f>IF(MIN(Class_0!O5,Class_1!O5,Class_2!O5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P26" s="5" t="str">
+        <f>IF(MIN(Class_0!P5,Class_1!P5,Class_2!P5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q26" s="5" t="str">
+        <f>IF(MIN(Class_0!Q5,Class_1!Q5,Class_2!Q5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R26" s="5" t="str">
+        <f>IF(MIN(Class_0!R5,Class_1!R5,Class_2!R5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S26" s="5" t="str">
+        <f>IF(MIN(Class_0!S5,Class_1!S5,Class_2!S5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T26" s="5" t="str">
+        <f>IF(MIN(Class_0!T5,Class_1!T5,Class_2!T5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U26" s="5" t="str">
+        <f>IF(MIN(Class_0!U5,Class_1!U5,Class_2!U5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="5" t="str">
+        <f>IF(MIN(Class_0!B6,Class_1!B6,Class_2!B6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C27" s="5" t="str">
+        <f>IF(MIN(Class_0!C6,Class_1!C6,Class_2!C6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="D27" s="5" t="str">
+        <f>IF(MIN(Class_0!D6,Class_1!D6,Class_2!D6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E27" s="5" t="str">
+        <f>IF(MIN(Class_0!E6,Class_1!E6,Class_2!E6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F27" s="5" t="str">
+        <f>IF(MIN(Class_0!F6,Class_1!F6,Class_2!F6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G27" s="5" t="str">
+        <f>IF(MIN(Class_0!G6,Class_1!G6,Class_2!G6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H27" s="5" t="str">
+        <f>IF(MIN(Class_0!H6,Class_1!H6,Class_2!H6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I27" s="5" t="str">
+        <f>IF(MIN(Class_0!I6,Class_1!I6,Class_2!I6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J27" s="5" t="str">
+        <f>IF(MIN(Class_0!J6,Class_1!J6,Class_2!J6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K27" s="5" t="str">
+        <f>IF(MIN(Class_0!K6,Class_1!K6,Class_2!K6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L27" s="5" t="str">
+        <f>IF(MIN(Class_0!L6,Class_1!L6,Class_2!L6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M27" s="5" t="str">
+        <f>IF(MIN(Class_0!M6,Class_1!M6,Class_2!M6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N27" s="5" t="str">
+        <f>IF(MIN(Class_0!N6,Class_1!N6,Class_2!N6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O27" s="5" t="str">
+        <f>IF(MIN(Class_0!O6,Class_1!O6,Class_2!O6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P27" s="5" t="str">
+        <f>IF(MIN(Class_0!P6,Class_1!P6,Class_2!P6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q27" s="5" t="str">
+        <f>IF(MIN(Class_0!Q6,Class_1!Q6,Class_2!Q6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R27" s="5" t="str">
+        <f>IF(MIN(Class_0!R6,Class_1!R6,Class_2!R6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S27" s="5" t="str">
+        <f>IF(MIN(Class_0!S6,Class_1!S6,Class_2!S6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T27" s="5" t="str">
+        <f>IF(MIN(Class_0!T6,Class_1!T6,Class_2!T6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U27" s="5" t="str">
+        <f>IF(MIN(Class_0!U6,Class_1!U6,Class_2!U6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="5" t="str">
+        <f>IF(MIN(Class_0!B7,Class_1!B7,Class_2!B7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C28" s="5" t="str">
+        <f>IF(MIN(Class_0!C7,Class_1!C7,Class_2!C7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D28" s="5" t="str">
+        <f>IF(MIN(Class_0!D7,Class_1!D7,Class_2!D7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E28" s="5" t="str">
+        <f>IF(MIN(Class_0!E7,Class_1!E7,Class_2!E7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F28" s="5" t="str">
+        <f>IF(MIN(Class_0!F7,Class_1!F7,Class_2!F7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G28" s="5" t="str">
+        <f>IF(MIN(Class_0!G7,Class_1!G7,Class_2!G7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H28" s="5" t="str">
+        <f>IF(MIN(Class_0!H7,Class_1!H7,Class_2!H7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I28" s="5" t="str">
+        <f>IF(MIN(Class_0!I7,Class_1!I7,Class_2!I7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J28" s="5" t="str">
+        <f>IF(MIN(Class_0!J7,Class_1!J7,Class_2!J7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K28" s="5" t="str">
+        <f>IF(MIN(Class_0!K7,Class_1!K7,Class_2!K7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L28" s="5" t="str">
+        <f>IF(MIN(Class_0!L7,Class_1!L7,Class_2!L7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M28" s="5" t="str">
+        <f>IF(MIN(Class_0!M7,Class_1!M7,Class_2!M7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N28" s="5" t="str">
+        <f>IF(MIN(Class_0!N7,Class_1!N7,Class_2!N7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O28" s="5" t="str">
+        <f>IF(MIN(Class_0!O7,Class_1!O7,Class_2!O7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P28" s="5" t="str">
+        <f>IF(MIN(Class_0!P7,Class_1!P7,Class_2!P7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q28" s="5" t="str">
+        <f>IF(MIN(Class_0!Q7,Class_1!Q7,Class_2!Q7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R28" s="5" t="str">
+        <f>IF(MIN(Class_0!R7,Class_1!R7,Class_2!R7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S28" s="5" t="str">
+        <f>IF(MIN(Class_0!S7,Class_1!S7,Class_2!S7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T28" s="5" t="str">
+        <f>IF(MIN(Class_0!T7,Class_1!T7,Class_2!T7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U28" s="5" t="str">
+        <f>IF(MIN(Class_0!U7,Class_1!U7,Class_2!U7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="5" t="str">
+        <f>IF(MIN(Class_0!B8,Class_1!B8,Class_2!B8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C29" s="5" t="str">
+        <f>IF(MIN(Class_0!C8,Class_1!C8,Class_2!C8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="D29" s="5" t="str">
+        <f>IF(MIN(Class_0!D8,Class_1!D8,Class_2!D8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E29" s="5" t="str">
+        <f>IF(MIN(Class_0!E8,Class_1!E8,Class_2!E8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F29" s="5" t="str">
+        <f>IF(MIN(Class_0!F8,Class_1!F8,Class_2!F8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G29" s="5" t="str">
+        <f>IF(MIN(Class_0!G8,Class_1!G8,Class_2!G8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H29" s="5" t="str">
+        <f>IF(MIN(Class_0!H8,Class_1!H8,Class_2!H8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I29" s="5" t="str">
+        <f>IF(MIN(Class_0!I8,Class_1!I8,Class_2!I8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J29" s="5" t="str">
+        <f>IF(MIN(Class_0!J8,Class_1!J8,Class_2!J8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K29" s="5" t="str">
+        <f>IF(MIN(Class_0!K8,Class_1!K8,Class_2!K8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L29" s="5" t="str">
+        <f>IF(MIN(Class_0!L8,Class_1!L8,Class_2!L8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M29" s="5" t="str">
+        <f>IF(MIN(Class_0!M8,Class_1!M8,Class_2!M8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N29" s="5" t="str">
+        <f>IF(MIN(Class_0!N8,Class_1!N8,Class_2!N8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O29" s="5" t="str">
+        <f>IF(MIN(Class_0!O8,Class_1!O8,Class_2!O8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P29" s="5" t="str">
+        <f>IF(MIN(Class_0!P8,Class_1!P8,Class_2!P8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q29" s="5" t="str">
+        <f>IF(MIN(Class_0!Q8,Class_1!Q8,Class_2!Q8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R29" s="5" t="str">
+        <f>IF(MIN(Class_0!R8,Class_1!R8,Class_2!R8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S29" s="5" t="str">
+        <f>IF(MIN(Class_0!S8,Class_1!S8,Class_2!S8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T29" s="5" t="str">
+        <f>IF(MIN(Class_0!T8,Class_1!T8,Class_2!T8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U29" s="5" t="str">
+        <f>IF(MIN(Class_0!U8,Class_1!U8,Class_2!U8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="5" t="str">
+        <f>IF(MIN(Class_0!B9,Class_1!B9,Class_2!B9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C30" s="5" t="str">
+        <f>IF(MIN(Class_0!C9,Class_1!C9,Class_2!C9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D30" s="5" t="str">
+        <f>IF(MIN(Class_0!D9,Class_1!D9,Class_2!D9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E30" s="5" t="str">
+        <f>IF(MIN(Class_0!E9,Class_1!E9,Class_2!E9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F30" s="5" t="str">
+        <f>IF(MIN(Class_0!F9,Class_1!F9,Class_2!F9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G30" s="5" t="str">
+        <f>IF(MIN(Class_0!G9,Class_1!G9,Class_2!G9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H30" s="5" t="str">
+        <f>IF(MIN(Class_0!H9,Class_1!H9,Class_2!H9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I30" s="5" t="str">
+        <f>IF(MIN(Class_0!I9,Class_1!I9,Class_2!I9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J30" s="5" t="str">
+        <f>IF(MIN(Class_0!J9,Class_1!J9,Class_2!J9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K30" s="5" t="str">
+        <f>IF(MIN(Class_0!K9,Class_1!K9,Class_2!K9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L30" s="5" t="str">
+        <f>IF(MIN(Class_0!L9,Class_1!L9,Class_2!L9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M30" s="5" t="str">
+        <f>IF(MIN(Class_0!M9,Class_1!M9,Class_2!M9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N30" s="5" t="str">
+        <f>IF(MIN(Class_0!N9,Class_1!N9,Class_2!N9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O30" s="5" t="str">
+        <f>IF(MIN(Class_0!O9,Class_1!O9,Class_2!O9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P30" s="5" t="str">
+        <f>IF(MIN(Class_0!P9,Class_1!P9,Class_2!P9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q30" s="5" t="str">
+        <f>IF(MIN(Class_0!Q9,Class_1!Q9,Class_2!Q9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R30" s="5" t="str">
+        <f>IF(MIN(Class_0!R9,Class_1!R9,Class_2!R9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S30" s="5" t="str">
+        <f>IF(MIN(Class_0!S9,Class_1!S9,Class_2!S9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T30" s="5" t="str">
+        <f>IF(MIN(Class_0!T9,Class_1!T9,Class_2!T9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U30" s="5" t="str">
+        <f>IF(MIN(Class_0!U9,Class_1!U9,Class_2!U9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="5" t="str">
+        <f>IF(MIN(Class_0!B10,Class_1!B10,Class_2!B10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C31" s="5" t="str">
+        <f>IF(MIN(Class_0!C10,Class_1!C10,Class_2!C10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D31" s="5" t="str">
+        <f>IF(MIN(Class_0!D10,Class_1!D10,Class_2!D10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E31" s="5" t="str">
+        <f>IF(MIN(Class_0!E10,Class_1!E10,Class_2!E10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F31" s="5" t="str">
+        <f>IF(MIN(Class_0!F10,Class_1!F10,Class_2!F10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G31" s="5" t="str">
+        <f>IF(MIN(Class_0!G10,Class_1!G10,Class_2!G10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H31" s="5" t="str">
+        <f>IF(MIN(Class_0!H10,Class_1!H10,Class_2!H10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I31" s="5" t="str">
+        <f>IF(MIN(Class_0!I10,Class_1!I10,Class_2!I10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J31" s="5" t="str">
+        <f>IF(MIN(Class_0!J10,Class_1!J10,Class_2!J10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K31" s="5" t="str">
+        <f>IF(MIN(Class_0!K10,Class_1!K10,Class_2!K10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L31" s="5" t="str">
+        <f>IF(MIN(Class_0!L10,Class_1!L10,Class_2!L10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M31" s="5" t="str">
+        <f>IF(MIN(Class_0!M10,Class_1!M10,Class_2!M10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N31" s="5" t="str">
+        <f>IF(MIN(Class_0!N10,Class_1!N10,Class_2!N10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O31" s="5" t="str">
+        <f>IF(MIN(Class_0!O10,Class_1!O10,Class_2!O10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P31" s="5" t="str">
+        <f>IF(MIN(Class_0!P10,Class_1!P10,Class_2!P10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q31" s="5" t="str">
+        <f>IF(MIN(Class_0!Q10,Class_1!Q10,Class_2!Q10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R31" s="5" t="str">
+        <f>IF(MIN(Class_0!R10,Class_1!R10,Class_2!R10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S31" s="5" t="str">
+        <f>IF(MIN(Class_0!S10,Class_1!S10,Class_2!S10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T31" s="5" t="str">
+        <f>IF(MIN(Class_0!T10,Class_1!T10,Class_2!T10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U31" s="5" t="str">
+        <f>IF(MIN(Class_0!U10,Class_1!U10,Class_2!U10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="5" t="str">
+        <f>IF(MIN(Class_0!B11,Class_1!B11,Class_2!B11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C32" s="5" t="str">
+        <f>IF(MIN(Class_0!C11,Class_1!C11,Class_2!C11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D32" s="5" t="str">
+        <f>IF(MIN(Class_0!D11,Class_1!D11,Class_2!D11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E32" s="5" t="str">
+        <f>IF(MIN(Class_0!E11,Class_1!E11,Class_2!E11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F32" s="5" t="str">
+        <f>IF(MIN(Class_0!F11,Class_1!F11,Class_2!F11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G32" s="5" t="str">
+        <f>IF(MIN(Class_0!G11,Class_1!G11,Class_2!G11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H32" s="5" t="str">
+        <f>IF(MIN(Class_0!H11,Class_1!H11,Class_2!H11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I32" s="5" t="str">
+        <f>IF(MIN(Class_0!I11,Class_1!I11,Class_2!I11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J32" s="5" t="str">
+        <f>IF(MIN(Class_0!J11,Class_1!J11,Class_2!J11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K32" s="5" t="str">
+        <f>IF(MIN(Class_0!K11,Class_1!K11,Class_2!K11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L32" s="5" t="str">
+        <f>IF(MIN(Class_0!L11,Class_1!L11,Class_2!L11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M32" s="5" t="str">
+        <f>IF(MIN(Class_0!M11,Class_1!M11,Class_2!M11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N32" s="5" t="str">
+        <f>IF(MIN(Class_0!N11,Class_1!N11,Class_2!N11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O32" s="5" t="str">
+        <f>IF(MIN(Class_0!O11,Class_1!O11,Class_2!O11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P32" s="5" t="str">
+        <f>IF(MIN(Class_0!P11,Class_1!P11,Class_2!P11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q32" s="5" t="str">
+        <f>IF(MIN(Class_0!Q11,Class_1!Q11,Class_2!Q11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R32" s="5" t="str">
+        <f>IF(MIN(Class_0!R11,Class_1!R11,Class_2!R11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S32" s="5" t="str">
+        <f>IF(MIN(Class_0!S11,Class_1!S11,Class_2!S11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T32" s="5" t="str">
+        <f>IF(MIN(Class_0!T11,Class_1!T11,Class_2!T11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U32" s="5" t="str">
+        <f>IF(MIN(Class_0!U11,Class_1!U11,Class_2!U11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="5" t="str">
+        <f>IF(MIN(Class_0!B12,Class_1!B12,Class_2!B12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C33" s="5" t="str">
+        <f>IF(MIN(Class_0!C12,Class_1!C12,Class_2!C12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D33" s="5" t="str">
+        <f>IF(MIN(Class_0!D12,Class_1!D12,Class_2!D12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E33" s="5" t="str">
+        <f>IF(MIN(Class_0!E12,Class_1!E12,Class_2!E12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F33" s="5" t="str">
+        <f>IF(MIN(Class_0!F12,Class_1!F12,Class_2!F12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G33" s="5" t="str">
+        <f>IF(MIN(Class_0!G12,Class_1!G12,Class_2!G12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H33" s="5" t="str">
+        <f>IF(MIN(Class_0!H12,Class_1!H12,Class_2!H12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I33" s="5" t="str">
+        <f>IF(MIN(Class_0!I12,Class_1!I12,Class_2!I12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J33" s="5" t="str">
+        <f>IF(MIN(Class_0!J12,Class_1!J12,Class_2!J12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K33" s="5" t="str">
+        <f>IF(MIN(Class_0!K12,Class_1!K12,Class_2!K12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L33" s="5" t="str">
+        <f>IF(MIN(Class_0!L12,Class_1!L12,Class_2!L12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M33" s="5" t="str">
+        <f>IF(MIN(Class_0!M12,Class_1!M12,Class_2!M12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N33" s="5" t="str">
+        <f>IF(MIN(Class_0!N12,Class_1!N12,Class_2!N12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O33" s="5" t="str">
+        <f>IF(MIN(Class_0!O12,Class_1!O12,Class_2!O12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P33" s="5" t="str">
+        <f>IF(MIN(Class_0!P12,Class_1!P12,Class_2!P12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q33" s="5" t="str">
+        <f>IF(MIN(Class_0!Q12,Class_1!Q12,Class_2!Q12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R33" s="5" t="str">
+        <f>IF(MIN(Class_0!R12,Class_1!R12,Class_2!R12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S33" s="5" t="str">
+        <f>IF(MIN(Class_0!S12,Class_1!S12,Class_2!S12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T33" s="5" t="str">
+        <f>IF(MIN(Class_0!T12,Class_1!T12,Class_2!T12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U33" s="5" t="str">
+        <f>IF(MIN(Class_0!U12,Class_1!U12,Class_2!U12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="5" t="str">
+        <f>IF(MIN(Class_0!B13,Class_1!B13,Class_2!B13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C34" s="5" t="str">
+        <f>IF(MIN(Class_0!C13,Class_1!C13,Class_2!C13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D34" s="5" t="str">
+        <f>IF(MIN(Class_0!D13,Class_1!D13,Class_2!D13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E34" s="5" t="str">
+        <f>IF(MIN(Class_0!E13,Class_1!E13,Class_2!E13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F34" s="5" t="str">
+        <f>IF(MIN(Class_0!F13,Class_1!F13,Class_2!F13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G34" s="5" t="str">
+        <f>IF(MIN(Class_0!G13,Class_1!G13,Class_2!G13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H34" s="5" t="str">
+        <f>IF(MIN(Class_0!H13,Class_1!H13,Class_2!H13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I34" s="5" t="str">
+        <f>IF(MIN(Class_0!I13,Class_1!I13,Class_2!I13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J34" s="5" t="str">
+        <f>IF(MIN(Class_0!J13,Class_1!J13,Class_2!J13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K34" s="5" t="str">
+        <f>IF(MIN(Class_0!K13,Class_1!K13,Class_2!K13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L34" s="5" t="str">
+        <f>IF(MIN(Class_0!L13,Class_1!L13,Class_2!L13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M34" s="5" t="str">
+        <f>IF(MIN(Class_0!M13,Class_1!M13,Class_2!M13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N34" s="5" t="str">
+        <f>IF(MIN(Class_0!N13,Class_1!N13,Class_2!N13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O34" s="5" t="str">
+        <f>IF(MIN(Class_0!O13,Class_1!O13,Class_2!O13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P34" s="5" t="str">
+        <f>IF(MIN(Class_0!P13,Class_1!P13,Class_2!P13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q34" s="5" t="str">
+        <f>IF(MIN(Class_0!Q13,Class_1!Q13,Class_2!Q13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R34" s="5" t="str">
+        <f>IF(MIN(Class_0!R13,Class_1!R13,Class_2!R13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S34" s="5" t="str">
+        <f>IF(MIN(Class_0!S13,Class_1!S13,Class_2!S13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T34" s="5" t="str">
+        <f>IF(MIN(Class_0!T13,Class_1!T13,Class_2!T13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U34" s="5" t="str">
+        <f>IF(MIN(Class_0!U13,Class_1!U13,Class_2!U13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="5" t="str">
+        <f>IF(MIN(Class_0!B14,Class_1!B14,Class_2!B14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="C35" s="5" t="str">
+        <f>IF(MIN(Class_0!C14,Class_1!C14,Class_2!C14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D35" s="5" t="str">
+        <f>IF(MIN(Class_0!D14,Class_1!D14,Class_2!D14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E35" s="5" t="str">
+        <f>IF(MIN(Class_0!E14,Class_1!E14,Class_2!E14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F35" s="5" t="str">
+        <f>IF(MIN(Class_0!F14,Class_1!F14,Class_2!F14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G35" s="5" t="str">
+        <f>IF(MIN(Class_0!G14,Class_1!G14,Class_2!G14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H35" s="5" t="str">
+        <f>IF(MIN(Class_0!H14,Class_1!H14,Class_2!H14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I35" s="5" t="str">
+        <f>IF(MIN(Class_0!I14,Class_1!I14,Class_2!I14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J35" s="5" t="str">
+        <f>IF(MIN(Class_0!J14,Class_1!J14,Class_2!J14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K35" s="5" t="str">
+        <f>IF(MIN(Class_0!K14,Class_1!K14,Class_2!K14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L35" s="5" t="str">
+        <f>IF(MIN(Class_0!L14,Class_1!L14,Class_2!L14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M35" s="5" t="str">
+        <f>IF(MIN(Class_0!M14,Class_1!M14,Class_2!M14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N35" s="5" t="str">
+        <f>IF(MIN(Class_0!N14,Class_1!N14,Class_2!N14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O35" s="5" t="str">
+        <f>IF(MIN(Class_0!O14,Class_1!O14,Class_2!O14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P35" s="5" t="str">
+        <f>IF(MIN(Class_0!P14,Class_1!P14,Class_2!P14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q35" s="5" t="str">
+        <f>IF(MIN(Class_0!Q14,Class_1!Q14,Class_2!Q14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R35" s="5" t="str">
+        <f>IF(MIN(Class_0!R14,Class_1!R14,Class_2!R14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S35" s="5" t="str">
+        <f>IF(MIN(Class_0!S14,Class_1!S14,Class_2!S14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T35" s="5" t="str">
+        <f>IF(MIN(Class_0!T14,Class_1!T14,Class_2!T14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U35" s="5" t="str">
+        <f>IF(MIN(Class_0!U14,Class_1!U14,Class_2!U14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="5" t="str">
+        <f>IF(MIN(Class_0!B15,Class_1!B15,Class_2!B15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C36" s="5" t="str">
+        <f>IF(MIN(Class_0!C15,Class_1!C15,Class_2!C15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D36" s="5" t="str">
+        <f>IF(MIN(Class_0!D15,Class_1!D15,Class_2!D15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E36" s="5" t="str">
+        <f>IF(MIN(Class_0!E15,Class_1!E15,Class_2!E15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F36" s="5" t="str">
+        <f>IF(MIN(Class_0!F15,Class_1!F15,Class_2!F15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G36" s="5" t="str">
+        <f>IF(MIN(Class_0!G15,Class_1!G15,Class_2!G15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H36" s="5" t="str">
+        <f>IF(MIN(Class_0!H15,Class_1!H15,Class_2!H15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I36" s="5" t="str">
+        <f>IF(MIN(Class_0!I15,Class_1!I15,Class_2!I15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J36" s="5" t="str">
+        <f>IF(MIN(Class_0!J15,Class_1!J15,Class_2!J15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K36" s="5" t="str">
+        <f>IF(MIN(Class_0!K15,Class_1!K15,Class_2!K15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L36" s="5" t="str">
+        <f>IF(MIN(Class_0!L15,Class_1!L15,Class_2!L15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M36" s="5" t="str">
+        <f>IF(MIN(Class_0!M15,Class_1!M15,Class_2!M15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N36" s="5" t="str">
+        <f>IF(MIN(Class_0!N15,Class_1!N15,Class_2!N15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O36" s="5" t="str">
+        <f>IF(MIN(Class_0!O15,Class_1!O15,Class_2!O15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P36" s="5" t="str">
+        <f>IF(MIN(Class_0!P15,Class_1!P15,Class_2!P15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q36" s="5" t="str">
+        <f>IF(MIN(Class_0!Q15,Class_1!Q15,Class_2!Q15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R36" s="5" t="str">
+        <f>IF(MIN(Class_0!R15,Class_1!R15,Class_2!R15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S36" s="5" t="str">
+        <f>IF(MIN(Class_0!S15,Class_1!S15,Class_2!S15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T36" s="5" t="str">
+        <f>IF(MIN(Class_0!T15,Class_1!T15,Class_2!T15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U36" s="5" t="str">
+        <f>IF(MIN(Class_0!U15,Class_1!U15,Class_2!U15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="5" t="str">
+        <f>IF(MIN(Class_0!B16,Class_1!B16,Class_2!B16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="C37" s="5" t="str">
+        <f>IF(MIN(Class_0!C16,Class_1!C16,Class_2!C16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D37" s="5" t="str">
+        <f>IF(MIN(Class_0!D16,Class_1!D16,Class_2!D16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E37" s="5" t="str">
+        <f>IF(MIN(Class_0!E16,Class_1!E16,Class_2!E16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F37" s="5" t="str">
+        <f>IF(MIN(Class_0!F16,Class_1!F16,Class_2!F16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G37" s="5" t="str">
+        <f>IF(MIN(Class_0!G16,Class_1!G16,Class_2!G16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H37" s="5" t="str">
+        <f>IF(MIN(Class_0!H16,Class_1!H16,Class_2!H16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I37" s="5" t="str">
+        <f>IF(MIN(Class_0!I16,Class_1!I16,Class_2!I16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J37" s="5" t="str">
+        <f>IF(MIN(Class_0!J16,Class_1!J16,Class_2!J16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K37" s="5" t="str">
+        <f>IF(MIN(Class_0!K16,Class_1!K16,Class_2!K16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L37" s="5" t="str">
+        <f>IF(MIN(Class_0!L16,Class_1!L16,Class_2!L16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M37" s="5" t="str">
+        <f>IF(MIN(Class_0!M16,Class_1!M16,Class_2!M16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N37" s="5" t="str">
+        <f>IF(MIN(Class_0!N16,Class_1!N16,Class_2!N16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O37" s="5" t="str">
+        <f>IF(MIN(Class_0!O16,Class_1!O16,Class_2!O16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P37" s="5" t="str">
+        <f>IF(MIN(Class_0!P16,Class_1!P16,Class_2!P16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q37" s="5" t="str">
+        <f>IF(MIN(Class_0!Q16,Class_1!Q16,Class_2!Q16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R37" s="5" t="str">
+        <f>IF(MIN(Class_0!R16,Class_1!R16,Class_2!R16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S37" s="5" t="str">
+        <f>IF(MIN(Class_0!S16,Class_1!S16,Class_2!S16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T37" s="5" t="str">
+        <f>IF(MIN(Class_0!T16,Class_1!T16,Class_2!T16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U37" s="5" t="str">
+        <f>IF(MIN(Class_0!U16,Class_1!U16,Class_2!U16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="5" t="str">
+        <f>IF(MIN(Class_0!B17,Class_1!B17,Class_2!B17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="C38" s="5" t="str">
+        <f>IF(MIN(Class_0!C17,Class_1!C17,Class_2!C17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D38" s="5" t="str">
+        <f>IF(MIN(Class_0!D17,Class_1!D17,Class_2!D17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E38" s="5" t="str">
+        <f>IF(MIN(Class_0!E17,Class_1!E17,Class_2!E17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F38" s="5" t="str">
+        <f>IF(MIN(Class_0!F17,Class_1!F17,Class_2!F17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G38" s="5" t="str">
+        <f>IF(MIN(Class_0!G17,Class_1!G17,Class_2!G17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H38" s="5" t="str">
+        <f>IF(MIN(Class_0!H17,Class_1!H17,Class_2!H17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I38" s="5" t="str">
+        <f>IF(MIN(Class_0!I17,Class_1!I17,Class_2!I17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J38" s="5" t="str">
+        <f>IF(MIN(Class_0!J17,Class_1!J17,Class_2!J17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K38" s="5" t="str">
+        <f>IF(MIN(Class_0!K17,Class_1!K17,Class_2!K17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L38" s="5" t="str">
+        <f>IF(MIN(Class_0!L17,Class_1!L17,Class_2!L17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M38" s="5" t="str">
+        <f>IF(MIN(Class_0!M17,Class_1!M17,Class_2!M17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N38" s="5" t="str">
+        <f>IF(MIN(Class_0!N17,Class_1!N17,Class_2!N17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O38" s="5" t="str">
+        <f>IF(MIN(Class_0!O17,Class_1!O17,Class_2!O17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P38" s="5" t="str">
+        <f>IF(MIN(Class_0!P17,Class_1!P17,Class_2!P17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q38" s="5" t="str">
+        <f>IF(MIN(Class_0!Q17,Class_1!Q17,Class_2!Q17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R38" s="5" t="str">
+        <f>IF(MIN(Class_0!R17,Class_1!R17,Class_2!R17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S38" s="5" t="str">
+        <f>IF(MIN(Class_0!S17,Class_1!S17,Class_2!S17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T38" s="5" t="str">
+        <f>IF(MIN(Class_0!T17,Class_1!T17,Class_2!T17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U38" s="5" t="str">
+        <f>IF(MIN(Class_0!U17,Class_1!U17,Class_2!U17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="5" t="str">
+        <f>IF(MIN(Class_0!B18,Class_1!B18,Class_2!B18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="C39" s="5" t="str">
+        <f>IF(MIN(Class_0!C18,Class_1!C18,Class_2!C18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D39" s="5" t="str">
+        <f>IF(MIN(Class_0!D18,Class_1!D18,Class_2!D18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E39" s="5" t="str">
+        <f>IF(MIN(Class_0!E18,Class_1!E18,Class_2!E18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F39" s="5" t="str">
+        <f>IF(MIN(Class_0!F18,Class_1!F18,Class_2!F18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G39" s="5" t="str">
+        <f>IF(MIN(Class_0!G18,Class_1!G18,Class_2!G18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H39" s="5" t="str">
+        <f>IF(MIN(Class_0!H18,Class_1!H18,Class_2!H18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I39" s="5" t="str">
+        <f>IF(MIN(Class_0!I18,Class_1!I18,Class_2!I18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J39" s="5" t="str">
+        <f>IF(MIN(Class_0!J18,Class_1!J18,Class_2!J18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K39" s="5" t="str">
+        <f>IF(MIN(Class_0!K18,Class_1!K18,Class_2!K18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L39" s="5" t="str">
+        <f>IF(MIN(Class_0!L18,Class_1!L18,Class_2!L18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M39" s="5" t="str">
+        <f>IF(MIN(Class_0!M18,Class_1!M18,Class_2!M18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N39" s="5" t="str">
+        <f>IF(MIN(Class_0!N18,Class_1!N18,Class_2!N18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O39" s="5" t="str">
+        <f>IF(MIN(Class_0!O18,Class_1!O18,Class_2!O18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P39" s="5" t="str">
+        <f>IF(MIN(Class_0!P18,Class_1!P18,Class_2!P18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q39" s="5" t="str">
+        <f>IF(MIN(Class_0!Q18,Class_1!Q18,Class_2!Q18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R39" s="5" t="str">
+        <f>IF(MIN(Class_0!R18,Class_1!R18,Class_2!R18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S39" s="5" t="str">
+        <f>IF(MIN(Class_0!S18,Class_1!S18,Class_2!S18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T39" s="5" t="str">
+        <f>IF(MIN(Class_0!T18,Class_1!T18,Class_2!T18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U39" s="5" t="str">
+        <f>IF(MIN(Class_0!U18,Class_1!U18,Class_2!U18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="5" t="str">
+        <f>IF(MIN(Class_0!B19,Class_1!B19,Class_2!B19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="C40" s="5" t="str">
+        <f>IF(MIN(Class_0!C19,Class_1!C19,Class_2!C19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="D40" s="5" t="str">
+        <f>IF(MIN(Class_0!D19,Class_1!D19,Class_2!D19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E40" s="5" t="str">
+        <f>IF(MIN(Class_0!E19,Class_1!E19,Class_2!E19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F40" s="5" t="str">
+        <f>IF(MIN(Class_0!F19,Class_1!F19,Class_2!F19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G40" s="5" t="str">
+        <f>IF(MIN(Class_0!G19,Class_1!G19,Class_2!G19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H40" s="5" t="str">
+        <f>IF(MIN(Class_0!H19,Class_1!H19,Class_2!H19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I40" s="5" t="str">
+        <f>IF(MIN(Class_0!I19,Class_1!I19,Class_2!I19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J40" s="5" t="str">
+        <f>IF(MIN(Class_0!J19,Class_1!J19,Class_2!J19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K40" s="5" t="str">
+        <f>IF(MIN(Class_0!K19,Class_1!K19,Class_2!K19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L40" s="5" t="str">
+        <f>IF(MIN(Class_0!L19,Class_1!L19,Class_2!L19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M40" s="5" t="str">
+        <f>IF(MIN(Class_0!M19,Class_1!M19,Class_2!M19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N40" s="5" t="str">
+        <f>IF(MIN(Class_0!N19,Class_1!N19,Class_2!N19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O40" s="5" t="str">
+        <f>IF(MIN(Class_0!O19,Class_1!O19,Class_2!O19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P40" s="5" t="str">
+        <f>IF(MIN(Class_0!P19,Class_1!P19,Class_2!P19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q40" s="5" t="str">
+        <f>IF(MIN(Class_0!Q19,Class_1!Q19,Class_2!Q19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R40" s="5" t="str">
+        <f>IF(MIN(Class_0!R19,Class_1!R19,Class_2!R19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S40" s="5" t="str">
+        <f>IF(MIN(Class_0!S19,Class_1!S19,Class_2!S19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T40" s="5" t="str">
+        <f>IF(MIN(Class_0!T19,Class_1!T19,Class_2!T19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U40" s="5" t="str">
+        <f>IF(MIN(Class_0!U19,Class_1!U19,Class_2!U19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="5" t="str">
+        <f>IF(MIN(Class_0!B20,Class_1!B20,Class_2!B20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="C41" s="5" t="str">
+        <f>IF(MIN(Class_0!C20,Class_1!C20,Class_2!C20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D41" s="5" t="str">
+        <f>IF(MIN(Class_0!D20,Class_1!D20,Class_2!D20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E41" s="5" t="str">
+        <f>IF(MIN(Class_0!E20,Class_1!E20,Class_2!E20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F41" s="5" t="str">
+        <f>IF(MIN(Class_0!F20,Class_1!F20,Class_2!F20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G41" s="5" t="str">
+        <f>IF(MIN(Class_0!G20,Class_1!G20,Class_2!G20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H41" s="5" t="str">
+        <f>IF(MIN(Class_0!H20,Class_1!H20,Class_2!H20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I41" s="5" t="str">
+        <f>IF(MIN(Class_0!I20,Class_1!I20,Class_2!I20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J41" s="5" t="str">
+        <f>IF(MIN(Class_0!J20,Class_1!J20,Class_2!J20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K41" s="5" t="str">
+        <f>IF(MIN(Class_0!K20,Class_1!K20,Class_2!K20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L41" s="5" t="str">
+        <f>IF(MIN(Class_0!L20,Class_1!L20,Class_2!L20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M41" s="5" t="str">
+        <f>IF(MIN(Class_0!M20,Class_1!M20,Class_2!M20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N41" s="5" t="str">
+        <f>IF(MIN(Class_0!N20,Class_1!N20,Class_2!N20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O41" s="5" t="str">
+        <f>IF(MIN(Class_0!O20,Class_1!O20,Class_2!O20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P41" s="5" t="str">
+        <f>IF(MIN(Class_0!P20,Class_1!P20,Class_2!P20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q41" s="5" t="str">
+        <f>IF(MIN(Class_0!Q20,Class_1!Q20,Class_2!Q20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R41" s="5" t="str">
+        <f>IF(MIN(Class_0!R20,Class_1!R20,Class_2!R20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S41" s="5" t="str">
+        <f>IF(MIN(Class_0!S20,Class_1!S20,Class_2!S20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T41" s="5" t="str">
+        <f>IF(MIN(Class_0!T20,Class_1!T20,Class_2!T20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U41" s="5" t="str">
+        <f>IF(MIN(Class_0!U20,Class_1!U20,Class_2!U20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="5" t="str">
+        <f>IF(MIN(Class_0!B21,Class_1!B21,Class_2!B21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="C42" s="5" t="str">
+        <f>IF(MIN(Class_0!C21,Class_1!C21,Class_2!C21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="D42" s="5" t="str">
+        <f>IF(MIN(Class_0!D21,Class_1!D21,Class_2!D21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E42" s="5" t="str">
+        <f>IF(MIN(Class_0!E21,Class_1!E21,Class_2!E21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F42" s="5" t="str">
+        <f>IF(MIN(Class_0!F21,Class_1!F21,Class_2!F21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G42" s="5" t="str">
+        <f>IF(MIN(Class_0!G21,Class_1!G21,Class_2!G21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H42" s="5" t="str">
+        <f>IF(MIN(Class_0!H21,Class_1!H21,Class_2!H21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I42" s="5" t="str">
+        <f>IF(MIN(Class_0!I21,Class_1!I21,Class_2!I21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J42" s="5" t="str">
+        <f>IF(MIN(Class_0!J21,Class_1!J21,Class_2!J21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K42" s="5" t="str">
+        <f>IF(MIN(Class_0!K21,Class_1!K21,Class_2!K21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L42" s="5" t="str">
+        <f>IF(MIN(Class_0!L21,Class_1!L21,Class_2!L21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M42" s="5" t="str">
+        <f>IF(MIN(Class_0!M21,Class_1!M21,Class_2!M21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N42" s="5" t="str">
+        <f>IF(MIN(Class_0!N21,Class_1!N21,Class_2!N21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O42" s="5" t="str">
+        <f>IF(MIN(Class_0!O21,Class_1!O21,Class_2!O21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P42" s="5" t="str">
+        <f>IF(MIN(Class_0!P21,Class_1!P21,Class_2!P21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q42" s="5" t="str">
+        <f>IF(MIN(Class_0!Q21,Class_1!Q21,Class_2!Q21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R42" s="5" t="str">
+        <f>IF(MIN(Class_0!R21,Class_1!R21,Class_2!R21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S42" s="5" t="str">
+        <f>IF(MIN(Class_0!S21,Class_1!S21,Class_2!S21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T42" s="5" t="str">
+        <f>IF(MIN(Class_0!T21,Class_1!T21,Class_2!T21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U42" s="5" t="str">
+        <f>IF(MIN(Class_0!U21,Class_1!U21,Class_2!U21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="C7:T7">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:U42">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3882,6 +5744,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="28.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
